--- a/Outcome/Appendix/Tables/Transform_rate_sensitivity.xlsx
+++ b/Outcome/Appendix/Tables/Transform_rate_sensitivity.xlsx
@@ -95,19 +95,13 @@
     <t xml:space="preserve">Suppressed</t>
   </si>
   <si>
-    <t xml:space="preserve">Shigellosis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Syphilis</t>
   </si>
   <si>
     <t xml:space="preserve">Influenza</t>
   </si>
   <si>
-    <t xml:space="preserve">CA (HPV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dengue fever</t>
+    <t xml:space="preserve">Shigellosis</t>
   </si>
   <si>
     <t xml:space="preserve">Leptospirosis</t>
@@ -261,6 +255,12 @@
   </si>
   <si>
     <t xml:space="preserve">Hybrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA (HPV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dengue fever</t>
   </si>
   <si>
     <t xml:space="preserve">Genital herpes</t>
@@ -668,13 +668,13 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -686,13 +686,13 @@
         <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.127</v>
+        <v>-0.119</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.107</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="3">
@@ -703,31 +703,31 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.036</v>
+        <v>-0.041</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.111</v>
+        <v>-0.091</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
       </c>
       <c r="F2"/>
       <c r="G2" t="n">
-        <v>0.043</v>
+        <v>-0.002</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.333</v>
+        <v>-0.338</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.173</v>
+        <v>-0.213</v>
       </c>
     </row>
     <row r="3">
@@ -813,13 +813,13 @@
       <c r="E3"/>
       <c r="F3"/>
       <c r="G3" t="n">
-        <v>-0.331</v>
+        <v>-0.296</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.219</v>
+        <v>-0.209</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.437</v>
+        <v>-0.472</v>
       </c>
     </row>
     <row r="4">
@@ -830,7 +830,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>25</v>
@@ -838,13 +838,13 @@
       <c r="E4"/>
       <c r="F4"/>
       <c r="G4" t="n">
-        <v>-0.17</v>
+        <v>-0.139</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.021</v>
+        <v>-0.135</v>
       </c>
       <c r="I4" t="n">
-        <v>0.066</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="5">
@@ -852,25 +852,21 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5"/>
+        <v>22</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1</v>
+      </c>
       <c r="F5"/>
-      <c r="G5" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.165</v>
-      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -883,130 +879,120 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E6"/>
       <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6"/>
-      <c r="I6"/>
+      <c r="G6" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.156</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.186</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7"/>
-      <c r="F7"/>
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" t="n">
-        <v>-0.175</v>
+        <v>0.042</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.146</v>
+        <v>0.072</v>
       </c>
       <c r="I7" t="n">
-        <v>0.096</v>
+        <v>0.072</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="F8"/>
-      <c r="G8" t="n">
-        <v>-0.099</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.13</v>
-      </c>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.261</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.308</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.308</v>
-      </c>
+        <v>-12</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10"/>
-      <c r="G10" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.018</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -1015,204 +1001,83 @@
         <v>22</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>16</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.057</v>
-      </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F12"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
       <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>-12</v>
-      </c>
-      <c r="F13"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13</v>
+      </c>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14"/>
-      <c r="G14" t="n">
-        <v>0.072</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.009</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.082</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>15</v>
-      </c>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>8</v>
-      </c>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>13</v>
-      </c>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
         <v>11</v>
       </c>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1230,79 +1095,79 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>49</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>53</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>54</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>55</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>56</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>57</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>58</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>59</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>60</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>62</v>
       </c>
       <c r="AA1" t="s">
         <v>2</v>
@@ -1311,25 +1176,25 @@
         <v>3</v>
       </c>
       <c r="AC1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE1" t="s">
         <v>63</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>64</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>65</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>66</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>67</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>69</v>
       </c>
       <c r="AJ1" t="s">
         <v>4</v>
@@ -1340,19 +1205,19 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
         <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" t="s">
-        <v>73</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -1362,28 +1227,28 @@
       </c>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.75</v>
+        <v>0.705</v>
       </c>
       <c r="K2" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="L2" t="n">
-        <v>0.455</v>
+        <v>0.415</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>17.95</v>
+        <v>28.7</v>
       </c>
       <c r="P2" t="n">
-        <v>66</v>
+        <v>69.15</v>
       </c>
       <c r="Q2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -1392,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s">
         <v>22</v>
@@ -1427,13 +1292,13 @@
       </c>
       <c r="AF2"/>
       <c r="AG2" t="n">
-        <v>0.0432</v>
+        <v>-0.00180000000000002</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.3334</v>
+        <v>-0.3384</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1734</v>
+        <v>-0.2134</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -1444,16 +1309,16 @@
         <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -1464,28 +1329,28 @@
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="n">
-        <v>0.665</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="L3" t="n">
-        <v>0.335</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>67.1</v>
+        <v>67.525</v>
       </c>
       <c r="O3" t="n">
-        <v>69</v>
+        <v>61.25</v>
       </c>
       <c r="P3" t="n">
-        <v>69</v>
+        <v>69.8</v>
       </c>
       <c r="Q3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -1494,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U3" t="s">
         <v>23</v>
@@ -1523,13 +1388,13 @@
       <c r="AE3"/>
       <c r="AF3"/>
       <c r="AG3" t="n">
-        <v>-0.3312</v>
+        <v>-0.2962</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.2194</v>
+        <v>-0.2094</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.4368</v>
+        <v>-0.4718</v>
       </c>
       <c r="AJ3" t="b">
         <v>0</v>
@@ -1540,16 +1405,16 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
@@ -1560,28 +1425,28 @@
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="n">
-        <v>0.545</v>
+        <v>0.29</v>
       </c>
       <c r="K4" t="n">
-        <v>0.33</v>
+        <v>0.165</v>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0.495</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="P4" t="n">
         <v>67</v>
       </c>
       <c r="Q4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1590,23 +1455,25 @@
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V4" t="n">
-        <v>31</v>
-      </c>
-      <c r="W4"/>
+        <v>34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>40</v>
+      </c>
       <c r="X4" t="n">
-        <v>0.7154</v>
+        <v>0.4288</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3514</v>
+        <v>0.2996</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.364</v>
+        <v>0.2996</v>
       </c>
       <c r="AA4" t="b">
         <v>1</v>
@@ -1619,13 +1486,13 @@
       <c r="AE4"/>
       <c r="AF4"/>
       <c r="AG4" t="n">
-        <v>-0.1704</v>
+        <v>-0.1388</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.0214</v>
+        <v>-0.1346</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.066</v>
+        <v>0.1954</v>
       </c>
       <c r="AJ4" t="b">
         <v>0</v>
@@ -1636,75 +1503,63 @@
         <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>43</v>
+      </c>
+      <c r="I5" t="n">
+        <v>71</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5" t="s">
         <v>77</v>
       </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>62</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P5" t="n">
-        <v>62</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>78</v>
-      </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>34</v>
-      </c>
-      <c r="W5" t="n">
-        <v>40</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="W5"/>
       <c r="X5" t="n">
-        <v>0.4288</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2996</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2996</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1712,19 +1567,17 @@
       <c r="AB5" t="b">
         <v>1</v>
       </c>
-      <c r="AC5"/>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
       <c r="AD5"/>
-      <c r="AE5"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
       <c r="AF5"/>
-      <c r="AG5" t="n">
-        <v>-0.0538</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.0896</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.1654</v>
-      </c>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
       <c r="AJ5" t="b">
         <v>0</v>
       </c>
@@ -1734,63 +1587,73 @@
         <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5.225</v>
+      </c>
+      <c r="N6" t="n">
+        <v>66</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="P6" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="s">
         <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="n">
-        <v>43</v>
-      </c>
-      <c r="I6" t="n">
-        <v>71</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6" t="s">
-        <v>79</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="s">
-        <v>73</v>
       </c>
       <c r="U6" t="s">
         <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="W6"/>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.7154</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.3514</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0.364</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1798,68 +1661,74 @@
       <c r="AB6" t="b">
         <v>1</v>
       </c>
-      <c r="AC6" t="n">
-        <v>-1</v>
-      </c>
+      <c r="AC6"/>
       <c r="AD6"/>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
+      <c r="AE6"/>
       <c r="AF6"/>
-      <c r="AG6"/>
-      <c r="AH6"/>
-      <c r="AI6"/>
+      <c r="AG6" t="n">
+        <v>-0.2654</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.1564</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.186</v>
+      </c>
       <c r="AJ6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7"/>
-      <c r="I7"/>
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>27</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32</v>
+      </c>
       <c r="J7" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0.205</v>
+        <v>0.845</v>
       </c>
       <c r="L7" t="n">
-        <v>0.46</v>
+        <v>0.845</v>
       </c>
       <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35</v>
+      </c>
+      <c r="O7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" t="n">
-        <v>59.925</v>
-      </c>
-      <c r="O7" t="n">
-        <v>8</v>
-      </c>
       <c r="P7" t="n">
-        <v>67</v>
+        <v>58.6</v>
       </c>
       <c r="Q7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1868,200 +1737,172 @@
         <v>1</v>
       </c>
       <c r="T7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V7" t="n">
-        <v>31</v>
-      </c>
-      <c r="W7"/>
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>32</v>
+      </c>
       <c r="X7" t="n">
-        <v>0.7154</v>
+        <v>0.8576</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3514</v>
+        <v>0.7734</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.364</v>
+        <v>0.7734</v>
       </c>
       <c r="AA7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AC7"/>
-      <c r="AD7"/>
-      <c r="AE7"/>
-      <c r="AF7"/>
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
       <c r="AG7" t="n">
-        <v>-0.1754</v>
+        <v>0.0424</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1464</v>
+        <v>0.0716</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.096</v>
+        <v>0.0716</v>
       </c>
       <c r="AJ7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" t="s">
         <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" t="s">
-        <v>73</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I8"/>
-      <c r="J8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M8" t="n">
-        <v>27</v>
-      </c>
-      <c r="N8" t="n">
-        <v>60</v>
-      </c>
-      <c r="O8" t="n">
-        <v>33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>57</v>
-      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
       <c r="Q8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>34</v>
-      </c>
-      <c r="W8" t="n">
-        <v>40</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="W8"/>
       <c r="X8" t="n">
-        <v>0.4288</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2996</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2996</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="AD8"/>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AF8"/>
-      <c r="AG8" t="n">
-        <v>-0.0988</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.1396</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.1296</v>
-      </c>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
       <c r="AJ8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
         <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
-      </c>
-      <c r="I9" t="n">
-        <v>67</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>69</v>
-      </c>
-      <c r="O9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>66.7</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
       <c r="Q9" t="s">
         <v>78</v>
       </c>
@@ -2069,28 +1910,26 @@
         <v>0</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>40</v>
-      </c>
-      <c r="W9" t="n">
-        <v>55</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="W9"/>
       <c r="X9" t="n">
-        <v>0.9556</v>
+        <v>0.8888</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.773</v>
+        <v>0.8888</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -2099,210 +1938,174 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AD9"/>
+      <c r="AE9" t="n">
         <v>12</v>
       </c>
-      <c r="AE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.2606</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-0.308</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.308</v>
-      </c>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9"/>
       <c r="AJ9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
         <v>70</v>
       </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
       <c r="F10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>41</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" t="n">
-        <v>42</v>
-      </c>
-      <c r="I10"/>
-      <c r="J10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="s">
+        <v>72</v>
+      </c>
+      <c r="U10" t="s">
+        <v>22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>28</v>
+      </c>
+      <c r="W10" t="n">
+        <v>35</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.9546</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P10" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>70</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" t="s">
-        <v>73</v>
-      </c>
-      <c r="U10" t="s">
-        <v>23</v>
-      </c>
-      <c r="V10" t="n">
-        <v>35</v>
-      </c>
-      <c r="W10"/>
-      <c r="X10" t="n">
-        <v>0.7228</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.3394</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.3834</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD10"/>
+      <c r="AD10" t="n">
+        <v>6</v>
+      </c>
       <c r="AE10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF10"/>
-      <c r="AG10" t="n">
-        <v>-0.0128</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.00559999999999999</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.0184</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10"/>
       <c r="AJ10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
         <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>35</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5.125</v>
-      </c>
-      <c r="P11" t="n">
-        <v>63.75</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
       <c r="Q11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R11" t="b">
         <v>0</v>
       </c>
       <c r="S11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U11" t="s">
         <v>22</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8576</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.7734</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.7734</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="b">
         <v>0</v>
@@ -2311,56 +2114,52 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
         <v>16</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>16</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.0566</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.0566</v>
-      </c>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11"/>
       <c r="AJ11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" t="n">
-        <v>58</v>
-      </c>
-      <c r="I12"/>
+        <v>28</v>
+      </c>
+      <c r="I12" t="n">
+        <v>44</v>
+      </c>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
@@ -2378,20 +2177,22 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
-        <v>68</v>
-      </c>
-      <c r="W12"/>
+        <v>28</v>
+      </c>
+      <c r="W12" t="n">
+        <v>36</v>
+      </c>
       <c r="X12" t="n">
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
@@ -2403,13 +2204,17 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AD12"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>8</v>
+      </c>
       <c r="AE12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF12"/>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>8</v>
+      </c>
       <c r="AG12"/>
       <c r="AH12"/>
       <c r="AI12"/>
@@ -2419,30 +2224,32 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" t="n">
-        <v>54</v>
-      </c>
-      <c r="I13"/>
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
       <c r="J13"/>
       <c r="K13"/>
       <c r="L13"/>
@@ -2451,7 +2258,7 @@
       <c r="O13"/>
       <c r="P13"/>
       <c r="Q13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -2460,23 +2267,25 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V13" t="n">
-        <v>66</v>
-      </c>
-      <c r="W13"/>
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7</v>
+      </c>
       <c r="X13" t="n">
-        <v>0.8888</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.8888</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="b">
         <v>0</v>
@@ -2485,13 +2294,17 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AD13"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13</v>
+      </c>
       <c r="AE13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF13"/>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>13</v>
+      </c>
       <c r="AG13"/>
       <c r="AH13"/>
       <c r="AI13"/>
@@ -2501,78 +2314,68 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>42</v>
-      </c>
-      <c r="I14"/>
-      <c r="J14" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>64.375</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I14" t="n">
+        <v>61</v>
+      </c>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
       <c r="Q14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="R14" t="b">
         <v>0</v>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V14" t="n">
-        <v>35</v>
-      </c>
-      <c r="W14"/>
+        <v>28</v>
+      </c>
+      <c r="W14" t="n">
+        <v>50</v>
+      </c>
       <c r="X14" t="n">
-        <v>0.7228</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3394</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3834</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="b">
         <v>0</v>
@@ -2581,90 +2384,102 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD14"/>
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11</v>
+      </c>
       <c r="AE14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF14"/>
-      <c r="AG14" t="n">
-        <v>0.0722</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-0.00939999999999996</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.0816</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14"/>
       <c r="AJ14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
         <v>75</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>72</v>
-      </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I15" t="n">
-        <v>41</v>
-      </c>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
+        <v>36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" t="n">
+        <v>63.75</v>
+      </c>
       <c r="Q15" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U15" t="s">
         <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W15" t="n">
         <v>35</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9546</v>
+        <v>0.7068</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9472</v>
+        <v>0.6284</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9472</v>
+        <v>0.6284</v>
       </c>
       <c r="AA15" t="b">
         <v>0</v>
@@ -2673,88 +2488,108 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG15"/>
-      <c r="AH15"/>
-      <c r="AI15"/>
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.0266000000000001</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0266000000000001</v>
+      </c>
       <c r="AJ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I16" t="n">
-        <v>48</v>
-      </c>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
+        <v>58</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>56</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>66.425</v>
+      </c>
       <c r="Q16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U16" t="s">
         <v>22</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="W16" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0.9556</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0.773</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>0.773</v>
       </c>
       <c r="AA16" t="b">
         <v>0</v>
@@ -2763,52 +2598,56 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG16"/>
-      <c r="AH16"/>
-      <c r="AI16"/>
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.2056</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.253</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.253</v>
+      </c>
       <c r="AJ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" t="s">
         <v>71</v>
       </c>
-      <c r="E17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" t="s">
-        <v>74</v>
-      </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
-      </c>
-      <c r="I17" t="n">
-        <v>44</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
@@ -2817,7 +2656,7 @@
       <c r="O17"/>
       <c r="P17"/>
       <c r="Q17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="R17" t="b">
         <v>0</v>
@@ -2826,25 +2665,23 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V17" t="n">
-        <v>28</v>
-      </c>
-      <c r="W17" t="n">
-        <v>36</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="W17"/>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.8888</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>0.8888</v>
       </c>
       <c r="AA17" t="b">
         <v>0</v>
@@ -2855,86 +2692,92 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
-        <v>8</v>
-      </c>
+      <c r="AD17"/>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
-      <c r="AF17" t="n">
-        <v>8</v>
-      </c>
+      <c r="AF17"/>
       <c r="AG17"/>
       <c r="AH17"/>
       <c r="AI17"/>
       <c r="AJ17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" t="s">
         <v>71</v>
       </c>
-      <c r="E18" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
-      </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
-      <c r="P18"/>
+        <v>35</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>46</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.425</v>
+      </c>
+      <c r="P18" t="n">
+        <v>66.575</v>
+      </c>
       <c r="Q18" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>7</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="W18"/>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0.7228</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0.3394</v>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>0.3834</v>
       </c>
       <c r="AA18" t="b">
         <v>0</v>
@@ -2945,49 +2788,51 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="n">
-        <v>13</v>
-      </c>
+      <c r="AD18"/>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
-      <c r="AF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG18"/>
-      <c r="AH18"/>
-      <c r="AI18"/>
+      <c r="AF18"/>
+      <c r="AG18" t="n">
+        <v>-0.0628</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.0134</v>
+      </c>
       <c r="AJ18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B19" t="s">
         <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
       </c>
       <c r="H19" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I19" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J19"/>
       <c r="K19"/>
@@ -3006,16 +2851,16 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U19" t="s">
         <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="W19" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -3033,102 +2878,88 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AG19"/>
       <c r="AH19"/>
       <c r="AI19"/>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
       </c>
       <c r="H20" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I20" t="n">
+        <v>61</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="s">
+        <v>72</v>
+      </c>
+      <c r="U20" t="s">
+        <v>22</v>
+      </c>
+      <c r="V20" t="n">
         <v>36</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40.5749999999999</v>
-      </c>
-      <c r="O20" t="n">
-        <v>24</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="W20" t="n">
         <v>58</v>
       </c>
-      <c r="Q20" t="s">
-        <v>70</v>
-      </c>
-      <c r="R20" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20" t="s">
-        <v>74</v>
-      </c>
-      <c r="U20" t="s">
-        <v>22</v>
-      </c>
-      <c r="V20" t="n">
-        <v>29</v>
-      </c>
-      <c r="W20" t="n">
-        <v>35</v>
-      </c>
       <c r="X20" t="n">
-        <v>0.7068</v>
+        <v>0.999</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6284</v>
+        <v>0.822</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.6284</v>
+        <v>0.822</v>
       </c>
       <c r="AA20" t="b">
         <v>0</v>
@@ -3140,51 +2971,45 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.0116000000000001</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.0116000000000001</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AG20"/>
+      <c r="AH20"/>
+      <c r="AI20"/>
       <c r="AJ20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
       </c>
       <c r="H21" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -3195,7 +3020,7 @@
       <c r="O21"/>
       <c r="P21"/>
       <c r="Q21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -3204,23 +3029,23 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U21" t="s">
         <v>23</v>
       </c>
       <c r="V21" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="W21"/>
       <c r="X21" t="n">
-        <v>0.8888</v>
+        <v>0.9226</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.8888</v>
+        <v>0.9226</v>
       </c>
       <c r="AA21" t="b">
         <v>0</v>
@@ -3245,31 +3070,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I22" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J22"/>
       <c r="K22"/>
@@ -3279,7 +3104,7 @@
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -3288,13 +3113,13 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U22" t="s">
         <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W22" t="n">
         <v>52</v>
@@ -3318,13 +3143,13 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22"/>
       <c r="AH22"/>
@@ -3335,31 +3160,31 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
         <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I23" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="J23"/>
       <c r="K23"/>
@@ -3369,7 +3194,7 @@
       <c r="O23"/>
       <c r="P23"/>
       <c r="Q23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -3378,25 +3203,25 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U23" t="s">
         <v>22</v>
       </c>
       <c r="V23" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="W23" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="X23" t="n">
-        <v>0.999</v>
+        <v>0.9546</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.822</v>
+        <v>0.9472</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.822</v>
+        <v>0.9472</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
@@ -3408,13 +3233,13 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG23"/>
       <c r="AH23"/>
@@ -3425,30 +3250,32 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>47</v>
-      </c>
-      <c r="I24"/>
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>32</v>
+      </c>
       <c r="J24"/>
       <c r="K24"/>
       <c r="L24"/>
@@ -3457,7 +3284,7 @@
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -3466,23 +3293,25 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V24" t="n">
-        <v>47</v>
-      </c>
-      <c r="W24"/>
+        <v>9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>33</v>
+      </c>
       <c r="X24" t="n">
-        <v>0.9226</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.9226</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="b">
         <v>0</v>
@@ -3493,11 +3322,15 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24"/>
+      <c r="AD24" t="n">
+        <v>-1</v>
+      </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
-      <c r="AF24"/>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
       <c r="AG24"/>
       <c r="AH24"/>
       <c r="AI24"/>
@@ -3507,32 +3340,30 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" t="n">
-        <v>38</v>
-      </c>
-      <c r="I25" t="n">
-        <v>52</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
       <c r="L25"/>
@@ -3541,7 +3372,7 @@
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -3550,22 +3381,20 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V25" t="n">
-        <v>38</v>
-      </c>
-      <c r="W25" t="n">
-        <v>52</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="W25"/>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>1</v>
@@ -3579,15 +3408,11 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD25"/>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF25"/>
       <c r="AG25"/>
       <c r="AH25"/>
       <c r="AI25"/>
@@ -3597,68 +3422,74 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" t="n">
-        <v>28</v>
-      </c>
-      <c r="I26" t="n">
-        <v>34</v>
-      </c>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
+        <v>88</v>
+      </c>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>4</v>
+      </c>
       <c r="Q26" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="U26" t="s">
-        <v>22</v>
-      </c>
-      <c r="V26" t="n">
-        <v>28</v>
-      </c>
-      <c r="W26" t="n">
-        <v>35</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="V26"/>
+      <c r="W26"/>
       <c r="X26" t="n">
-        <v>0.9546</v>
+        <v>0.4748</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.9472</v>
+        <v>0.4748</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.9472</v>
+        <v>0.5252</v>
       </c>
       <c r="AA26" t="b">
         <v>0</v>
@@ -3666,52 +3497,50 @@
       <c r="AB26" t="b">
         <v>0</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG26"/>
-      <c r="AH26"/>
-      <c r="AI26"/>
+      <c r="AC26"/>
+      <c r="AD26"/>
+      <c r="AE26"/>
+      <c r="AF26"/>
+      <c r="AG26" t="n">
+        <v>-0.3298</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.3298</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.3298</v>
+      </c>
       <c r="AJ26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
         <v>22</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J27"/>
       <c r="K27"/>
@@ -3721,7 +3550,7 @@
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
@@ -3730,16 +3559,16 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U27" t="s">
         <v>22</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="W27" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
@@ -3760,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG27"/>
       <c r="AH27"/>
@@ -3777,30 +3606,32 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>44</v>
-      </c>
-      <c r="I28"/>
+        <v>34</v>
+      </c>
+      <c r="I28" t="n">
+        <v>61</v>
+      </c>
       <c r="J28"/>
       <c r="K28"/>
       <c r="L28"/>
@@ -3809,7 +3640,7 @@
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -3818,23 +3649,25 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
-        <v>44</v>
-      </c>
-      <c r="W28"/>
+        <v>34</v>
+      </c>
+      <c r="W28" t="n">
+        <v>60</v>
+      </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.8354</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0.8354</v>
       </c>
       <c r="AA28" t="b">
         <v>0</v>
@@ -3845,11 +3678,15 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28"/>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
-      <c r="AF28"/>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
       <c r="AG28"/>
       <c r="AH28"/>
       <c r="AI28"/>
@@ -3859,74 +3696,60 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="H29"/>
       <c r="I29"/>
-      <c r="J29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>4</v>
-      </c>
+      <c r="J29"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
       <c r="Q29" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="U29" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="V29"/>
       <c r="W29"/>
       <c r="X29" t="n">
-        <v>0.4748</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4748</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.5252</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -3938,46 +3761,40 @@
       <c r="AD29"/>
       <c r="AE29"/>
       <c r="AF29"/>
-      <c r="AG29" t="n">
-        <v>-0.3448</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>-0.3448</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.3448</v>
-      </c>
+      <c r="AG29"/>
+      <c r="AH29"/>
+      <c r="AI29"/>
       <c r="AJ29" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
         <v>22</v>
       </c>
       <c r="H30" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="J30"/>
       <c r="K30"/>
@@ -3987,7 +3804,7 @@
       <c r="O30"/>
       <c r="P30"/>
       <c r="Q30" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
@@ -3996,16 +3813,16 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U30" t="s">
         <v>22</v>
       </c>
       <c r="V30" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
@@ -4026,13 +3843,13 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG30"/>
       <c r="AH30"/>
@@ -4043,68 +3860,78 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" t="n">
-        <v>34</v>
-      </c>
-      <c r="I31" t="n">
         <v>61</v>
       </c>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
+      <c r="I31"/>
+      <c r="J31" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>66</v>
+      </c>
+      <c r="O31" t="n">
+        <v>40.65</v>
+      </c>
+      <c r="P31" t="n">
+        <v>68</v>
+      </c>
       <c r="Q31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
       </c>
       <c r="S31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V31" t="n">
-        <v>34</v>
-      </c>
-      <c r="W31" t="n">
-        <v>60</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="W31"/>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0.812</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.8354</v>
+        <v>0.3324</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.8354</v>
+        <v>0.4796</v>
       </c>
       <c r="AA31" t="b">
         <v>0</v>
@@ -4115,46 +3942,52 @@
       <c r="AC31" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD31"/>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31"/>
-      <c r="AH31"/>
-      <c r="AI31"/>
+      <c r="AF31"/>
+      <c r="AG31" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>-0.1124</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.0654</v>
+      </c>
       <c r="AJ31" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32"/>
-      <c r="I32"/>
+        <v>22</v>
+      </c>
+      <c r="H32" t="n">
+        <v>28</v>
+      </c>
+      <c r="I32" t="n">
+        <v>54</v>
+      </c>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32"/>
@@ -4163,7 +3996,7 @@
       <c r="O32"/>
       <c r="P32"/>
       <c r="Q32" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R32" t="b">
         <v>0</v>
@@ -4172,18 +4005,22 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="U32" t="s">
-        <v>25</v>
-      </c>
-      <c r="V32"/>
-      <c r="W32"/>
+        <v>22</v>
+      </c>
+      <c r="V32" t="n">
+        <v>28</v>
+      </c>
+      <c r="W32" t="n">
+        <v>50</v>
+      </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
         <v>1</v>
@@ -4194,10 +4031,18 @@
       <c r="AB32" t="b">
         <v>0</v>
       </c>
-      <c r="AC32"/>
-      <c r="AD32"/>
-      <c r="AE32"/>
-      <c r="AF32"/>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>4</v>
+      </c>
       <c r="AG32"/>
       <c r="AH32"/>
       <c r="AI32"/>
@@ -4207,68 +4052,78 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="n">
+        <v>31</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>61</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q33" t="s">
         <v>76</v>
       </c>
-      <c r="E33" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" t="n">
-        <v>5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33" t="s">
-        <v>79</v>
-      </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
       <c r="S33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>7</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="W33"/>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0.7154</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>0.3514</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>0.364</v>
       </c>
       <c r="AA33" t="b">
         <v>0</v>
@@ -4279,96 +4134,88 @@
       <c r="AC33" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD33"/>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
+      <c r="AF33"/>
+      <c r="AG33" t="n">
+        <v>-0.0804</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>-0.0264</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>-0.054</v>
+      </c>
       <c r="AJ33" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" t="n">
-        <v>61</v>
-      </c>
-      <c r="I34"/>
-      <c r="J34" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="M34" t="n">
-        <v>5.825</v>
-      </c>
-      <c r="N34" t="n">
-        <v>66</v>
-      </c>
-      <c r="O34" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="P34" t="n">
-        <v>71</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="I34" t="n">
+        <v>55</v>
+      </c>
+      <c r="J34"/>
+      <c r="K34"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
       <c r="Q34" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V34" t="n">
-        <v>61</v>
-      </c>
-      <c r="W34"/>
+        <v>30</v>
+      </c>
+      <c r="W34" t="n">
+        <v>54</v>
+      </c>
       <c r="X34" t="n">
-        <v>0.812</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.3324</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.4796</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -4379,88 +4226,100 @@
       <c r="AC34" t="n">
         <v>0</v>
       </c>
-      <c r="AD34"/>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
-      <c r="AF34"/>
-      <c r="AG34" t="n">
-        <v>-0.042</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>-0.0574</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.0154</v>
-      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34"/>
+      <c r="AH34"/>
+      <c r="AI34"/>
       <c r="AJ34" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" t="n">
+        <v>43</v>
+      </c>
+      <c r="I35" t="n">
+        <v>57</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="M35" t="n">
+        <v>8</v>
+      </c>
+      <c r="N35" t="n">
+        <v>53</v>
+      </c>
+      <c r="O35" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q35" t="s">
         <v>76</v>
       </c>
-      <c r="E35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" t="n">
-        <v>28</v>
-      </c>
-      <c r="I35" t="n">
-        <v>54</v>
-      </c>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35" t="s">
-        <v>79</v>
-      </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U35" t="s">
         <v>22</v>
       </c>
       <c r="V35" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="W35" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.9556</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0.773</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0.773</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -4469,88 +4328,104 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
+        <v>2</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>-0.1156</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-0.178</v>
+      </c>
       <c r="AJ35" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H36" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" t="n">
-        <v>55</v>
-      </c>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
+        <v>48</v>
+      </c>
+      <c r="I36"/>
+      <c r="J36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="M36" t="n">
+        <v>37</v>
+      </c>
+      <c r="N36" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="O36" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>71</v>
+      </c>
       <c r="Q36" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
       <c r="S36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V36" t="n">
-        <v>30</v>
-      </c>
-      <c r="W36" t="n">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="W36"/>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0.9962</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0.2244</v>
       </c>
       <c r="Z36" t="n">
-        <v>1</v>
+        <v>0.7718</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -4561,100 +4436,98 @@
       <c r="AC36" t="n">
         <v>0</v>
       </c>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD36"/>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
-      <c r="AF36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG36"/>
-      <c r="AH36"/>
-      <c r="AI36"/>
+      <c r="AF36"/>
+      <c r="AG36" t="n">
+        <v>-0.00619999999999998</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>-0.0894</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.0831999999999999</v>
+      </c>
       <c r="AJ36" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" t="s">
         <v>71</v>
       </c>
-      <c r="E37" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" t="s">
-        <v>74</v>
-      </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" t="n">
-        <v>43</v>
-      </c>
-      <c r="I37" t="n">
-        <v>56</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I37"/>
       <c r="J37" t="n">
-        <v>0.85</v>
+        <v>0.715</v>
       </c>
       <c r="K37" t="n">
-        <v>0.675</v>
+        <v>0.375</v>
       </c>
       <c r="L37" t="n">
-        <v>0.675</v>
+        <v>0.34</v>
       </c>
       <c r="M37" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
       <c r="N37" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>54.8999999999999</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>68</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="s">
+        <v>71</v>
+      </c>
+      <c r="U37" t="s">
         <v>23</v>
       </c>
-      <c r="P37" t="n">
-        <v>66</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>78</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="s">
-        <v>74</v>
-      </c>
-      <c r="U37" t="s">
-        <v>22</v>
-      </c>
       <c r="V37" t="n">
-        <v>40</v>
-      </c>
-      <c r="W37" t="n">
-        <v>55</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="W37"/>
       <c r="X37" t="n">
-        <v>0.9556</v>
+        <v>0.7228</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.773</v>
+        <v>0.3394</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.773</v>
+        <v>0.3834</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -4663,25 +4536,21 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD37"/>
       <c r="AE37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37"/>
       <c r="AG37" t="n">
-        <v>-0.1056</v>
+        <v>-0.00780000000000003</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.098</v>
+        <v>0.0356</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.098</v>
+        <v>-0.0434</v>
       </c>
       <c r="AJ37" t="b">
         <v>0</v>
@@ -4689,78 +4558,68 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>48</v>
-      </c>
-      <c r="I38"/>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="M38" t="n">
-        <v>40</v>
-      </c>
-      <c r="N38" t="n">
-        <v>50</v>
-      </c>
-      <c r="O38" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="P38" t="n">
-        <v>71</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>53</v>
+      </c>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
       <c r="Q38" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
       <c r="S38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V38" t="n">
-        <v>48</v>
-      </c>
-      <c r="W38"/>
+        <v>36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>52</v>
+      </c>
       <c r="X38" t="n">
-        <v>0.9962</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.2244</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.7718</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="b">
         <v>0</v>
@@ -4771,42 +4630,40 @@
       <c r="AC38" t="n">
         <v>0</v>
       </c>
-      <c r="AD38"/>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
-      <c r="AF38"/>
-      <c r="AG38" t="n">
-        <v>0.00380000000000003</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>-0.1444</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.1482</v>
-      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38"/>
+      <c r="AH38"/>
+      <c r="AI38"/>
       <c r="AJ38" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
@@ -4815,7 +4672,7 @@
         <v>36</v>
       </c>
       <c r="I39" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J39"/>
       <c r="K39"/>
@@ -4825,7 +4682,7 @@
       <c r="O39"/>
       <c r="P39"/>
       <c r="Q39" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -4834,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U39" t="s">
         <v>22</v>
@@ -4843,16 +4700,16 @@
         <v>36</v>
       </c>
       <c r="W39" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0.822</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>0.822</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -4881,32 +4738,30 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
       </c>
       <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F40" t="s">
         <v>71</v>
       </c>
-      <c r="E40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F40" t="s">
-        <v>74</v>
-      </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H40" t="n">
-        <v>36</v>
-      </c>
-      <c r="I40" t="n">
-        <v>59</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I40"/>
       <c r="J40"/>
       <c r="K40"/>
       <c r="L40"/>
@@ -4915,7 +4770,7 @@
       <c r="O40"/>
       <c r="P40"/>
       <c r="Q40" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -4924,25 +4779,23 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V40" t="n">
-        <v>36</v>
-      </c>
-      <c r="W40" t="n">
-        <v>58</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="W40"/>
       <c r="X40" t="n">
-        <v>0.999</v>
+        <v>0.9226</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.822</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.822</v>
+        <v>0.9226</v>
       </c>
       <c r="AA40" t="b">
         <v>0</v>
@@ -4953,15 +4806,11 @@
       <c r="AC40" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AD40"/>
       <c r="AE40" t="n">
         <v>0</v>
       </c>
-      <c r="AF40" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF40"/>
       <c r="AG40"/>
       <c r="AH40"/>
       <c r="AI40"/>
@@ -4971,30 +4820,32 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>47</v>
-      </c>
-      <c r="I41"/>
+        <v>41</v>
+      </c>
+      <c r="I41" t="n">
+        <v>52</v>
+      </c>
       <c r="J41"/>
       <c r="K41"/>
       <c r="L41"/>
@@ -5003,7 +4854,7 @@
       <c r="O41"/>
       <c r="P41"/>
       <c r="Q41" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R41" t="b">
         <v>0</v>
@@ -5012,23 +4863,25 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V41" t="n">
-        <v>47</v>
-      </c>
-      <c r="W41"/>
+        <v>38</v>
+      </c>
+      <c r="W41" t="n">
+        <v>52</v>
+      </c>
       <c r="X41" t="n">
-        <v>0.9226</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.9226</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="b">
         <v>0</v>
@@ -5037,13 +4890,17 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41"/>
+        <v>3</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
       <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41"/>
+        <v>3</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
       <c r="AG41"/>
       <c r="AH41"/>
       <c r="AI41"/>
@@ -5053,68 +4910,82 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G42" t="s">
         <v>22</v>
       </c>
       <c r="H42" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>52</v>
-      </c>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
+        <v>30</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N42" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>59.85</v>
+      </c>
       <c r="Q42" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
       </c>
       <c r="S42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U42" t="s">
         <v>22</v>
       </c>
       <c r="V42" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="W42" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0.8576</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>0.7734</v>
       </c>
       <c r="Z42" t="n">
-        <v>1</v>
+        <v>0.7734</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -5123,75 +4994,77 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42"/>
-      <c r="AH42"/>
-      <c r="AI42"/>
+        <v>2</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>-0.0826</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>-0.1384</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-0.1384</v>
+      </c>
       <c r="AJ42" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11</v>
-      </c>
-      <c r="I43" t="n">
-        <v>33</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="H43"/>
+      <c r="I43"/>
       <c r="J43" t="n">
-        <v>0.72</v>
+        <v>0.645</v>
       </c>
       <c r="K43" t="n">
-        <v>0.52</v>
+        <v>0.645</v>
       </c>
       <c r="L43" t="n">
-        <v>0.52</v>
+        <v>0.355</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>46.425</v>
+        <v>25</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>68.425</v>
+        <v>29</v>
       </c>
       <c r="Q43" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
@@ -5200,25 +5073,21 @@
         <v>1</v>
       </c>
       <c r="T43" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="U43" t="s">
-        <v>22</v>
-      </c>
-      <c r="V43" t="n">
-        <v>11</v>
-      </c>
-      <c r="W43" t="n">
-        <v>32</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="V43"/>
+      <c r="W43"/>
       <c r="X43" t="n">
-        <v>0.8576</v>
+        <v>0.4748</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.7734</v>
+        <v>0.4748</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.7734</v>
+        <v>0.5252</v>
       </c>
       <c r="AA43" t="b">
         <v>0</v>
@@ -5226,26 +5095,18 @@
       <c r="AB43" t="b">
         <v>0</v>
       </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43"/>
+      <c r="AF43"/>
       <c r="AG43" t="n">
-        <v>-0.1376</v>
+        <v>0.1702</v>
       </c>
       <c r="AH43" t="n">
-        <v>-0.2534</v>
+        <v>0.1702</v>
       </c>
       <c r="AI43" t="n">
-        <v>-0.2534</v>
+        <v>-0.1702</v>
       </c>
       <c r="AJ43" t="b">
         <v>0</v>
@@ -5253,74 +5114,64 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
       </c>
       <c r="D44" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>70</v>
+      </c>
+      <c r="F44" t="s">
         <v>71</v>
       </c>
-      <c r="E44" t="s">
-        <v>72</v>
-      </c>
-      <c r="F44" t="s">
-        <v>87</v>
-      </c>
       <c r="G44" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44"/>
+        <v>23</v>
+      </c>
+      <c r="H44" t="n">
+        <v>68</v>
+      </c>
       <c r="I44"/>
-      <c r="J44" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="n">
-        <v>24.125</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>29</v>
-      </c>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
       <c r="Q44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="R44" t="b">
         <v>0</v>
       </c>
       <c r="S44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="U44" t="s">
-        <v>88</v>
-      </c>
-      <c r="V44"/>
+        <v>23</v>
+      </c>
+      <c r="V44" t="n">
+        <v>68</v>
+      </c>
       <c r="W44"/>
       <c r="X44" t="n">
-        <v>0.4748</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.4748</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.5252</v>
+        <v>1</v>
       </c>
       <c r="AA44" t="b">
         <v>0</v>
@@ -5328,49 +5179,49 @@
       <c r="AB44" t="b">
         <v>0</v>
       </c>
-      <c r="AC44"/>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
       <c r="AD44"/>
-      <c r="AE44"/>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
       <c r="AF44"/>
-      <c r="AG44" t="n">
-        <v>0.1052</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0.1052</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>-0.1052</v>
-      </c>
+      <c r="AG44"/>
+      <c r="AH44"/>
+      <c r="AI44"/>
       <c r="AJ44" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>68</v>
-      </c>
-      <c r="I45"/>
+        <v>34</v>
+      </c>
+      <c r="I45" t="n">
+        <v>60</v>
+      </c>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
@@ -5379,7 +5230,7 @@
       <c r="O45"/>
       <c r="P45"/>
       <c r="Q45" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -5388,23 +5239,25 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V45" t="n">
-        <v>68</v>
-      </c>
-      <c r="W45"/>
+        <v>34</v>
+      </c>
+      <c r="W45" t="n">
+        <v>60</v>
+      </c>
       <c r="X45" t="n">
         <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.8354</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
+        <v>0.8354</v>
       </c>
       <c r="AA45" t="b">
         <v>0</v>
@@ -5415,11 +5268,15 @@
       <c r="AC45" t="n">
         <v>0</v>
       </c>
-      <c r="AD45"/>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
       <c r="AE45" t="n">
         <v>0</v>
       </c>
-      <c r="AF45"/>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
       <c r="AG45"/>
       <c r="AH45"/>
       <c r="AI45"/>
@@ -5429,32 +5286,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F46" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" t="n">
-        <v>34</v>
-      </c>
-      <c r="I46" t="n">
-        <v>60</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H46"/>
+      <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
       <c r="L46"/>
@@ -5463,7 +5316,7 @@
       <c r="O46"/>
       <c r="P46"/>
       <c r="Q46" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -5472,25 +5325,21 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="U46" t="s">
-        <v>22</v>
-      </c>
-      <c r="V46" t="n">
-        <v>34</v>
-      </c>
-      <c r="W46" t="n">
-        <v>60</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="V46"/>
+      <c r="W46"/>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.8354</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.8354</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="b">
         <v>0</v>
@@ -5498,18 +5347,10 @@
       <c r="AB46" t="b">
         <v>0</v>
       </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
       <c r="AG46"/>
       <c r="AH46"/>
       <c r="AI46"/>
@@ -5519,60 +5360,78 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
       </c>
       <c r="D47" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" t="s">
         <v>71</v>
       </c>
-      <c r="E47" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" t="s">
-        <v>25</v>
-      </c>
       <c r="G47" t="s">
-        <v>25</v>
-      </c>
-      <c r="H47"/>
+        <v>23</v>
+      </c>
+      <c r="H47" t="n">
+        <v>61</v>
+      </c>
       <c r="I47"/>
-      <c r="J47"/>
-      <c r="K47"/>
-      <c r="L47"/>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47"/>
-      <c r="P47"/>
+      <c r="J47" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="M47" t="n">
+        <v>8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>66</v>
+      </c>
+      <c r="O47" t="n">
+        <v>61</v>
+      </c>
+      <c r="P47" t="n">
+        <v>70</v>
+      </c>
       <c r="Q47" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R47" t="b">
         <v>0</v>
       </c>
       <c r="S47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="U47" t="s">
-        <v>25</v>
-      </c>
-      <c r="V47"/>
+        <v>23</v>
+      </c>
+      <c r="V47" t="n">
+        <v>61</v>
+      </c>
       <c r="W47"/>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.812</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>0.4796</v>
       </c>
       <c r="AA47" t="b">
         <v>0</v>
@@ -5580,66 +5439,78 @@
       <c r="AB47" t="b">
         <v>0</v>
       </c>
-      <c r="AC47"/>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
       <c r="AD47"/>
-      <c r="AE47"/>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
       <c r="AF47"/>
-      <c r="AG47"/>
-      <c r="AH47"/>
-      <c r="AI47"/>
+      <c r="AG47" t="n">
+        <v>0.0479999999999999</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>-0.0324</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.0804</v>
+      </c>
       <c r="AJ47" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" t="n">
-        <v>61</v>
-      </c>
-      <c r="I48"/>
+        <v>31</v>
+      </c>
+      <c r="I48" t="n">
+        <v>37</v>
+      </c>
       <c r="J48" t="n">
-        <v>0.785</v>
+        <v>0.325</v>
       </c>
       <c r="K48" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="L48" t="n">
-        <v>0.435</v>
+        <v>0.21</v>
       </c>
       <c r="M48" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O48" t="n">
-        <v>18.7</v>
+        <v>33</v>
       </c>
       <c r="P48" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Q48" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
@@ -5648,23 +5519,25 @@
         <v>1</v>
       </c>
       <c r="T48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="V48" t="n">
-        <v>61</v>
-      </c>
-      <c r="W48"/>
+        <v>34</v>
+      </c>
+      <c r="W48" t="n">
+        <v>40</v>
+      </c>
       <c r="X48" t="n">
-        <v>0.812</v>
+        <v>0.4288</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.3324</v>
+        <v>0.2996</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.4796</v>
+        <v>0.2996</v>
       </c>
       <c r="AA48" t="b">
         <v>0</v>
@@ -5673,21 +5546,25 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48"/>
+        <v>-3</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>-3</v>
+      </c>
       <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48"/>
+        <v>3</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3</v>
+      </c>
       <c r="AG48" t="n">
-        <v>-0.027</v>
+        <v>-0.1038</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.0176</v>
+        <v>-0.0896</v>
       </c>
       <c r="AI48" t="n">
-        <v>-0.0446</v>
+        <v>-0.0896</v>
       </c>
       <c r="AJ48" t="b">
         <v>0</v>
@@ -5698,19 +5575,19 @@
         <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G49" t="s">
         <v>22</v>
@@ -5729,7 +5606,7 @@
       <c r="O49"/>
       <c r="P49"/>
       <c r="Q49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
@@ -5738,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U49" t="s">
         <v>22</v>
@@ -5799,58 +5676,58 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>49</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>53</v>
-      </c>
-      <c r="R1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2">
@@ -5858,19 +5735,19 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
         <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -5911,19 +5788,19 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -5935,28 +5812,28 @@
         <v>36</v>
       </c>
       <c r="J3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>0.64</v>
+        <v>0.655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.64</v>
+        <v>0.655</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
       </c>
       <c r="N3" t="n">
-        <v>40.5749999999999</v>
+        <v>49.55</v>
       </c>
       <c r="O3" t="n">
         <v>24</v>
       </c>
       <c r="P3" t="n">
-        <v>58</v>
+        <v>63.75</v>
       </c>
       <c r="Q3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -5970,19 +5847,19 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
         <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" t="s">
-        <v>73</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -5992,28 +5869,28 @@
       </c>
       <c r="I4"/>
       <c r="J4" t="n">
-        <v>0.75</v>
+        <v>0.705</v>
       </c>
       <c r="K4" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="L4" t="n">
-        <v>0.455</v>
+        <v>0.415</v>
       </c>
       <c r="M4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="O4" t="n">
-        <v>17.95</v>
+        <v>28.7</v>
       </c>
       <c r="P4" t="n">
-        <v>66</v>
+        <v>69.15</v>
       </c>
       <c r="Q4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -6024,22 +5901,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
         <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -6077,55 +5954,55 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="n">
+        <v>43</v>
+      </c>
+      <c r="I6" t="n">
+        <v>58</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>56</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.425</v>
+      </c>
+      <c r="Q6" t="s">
         <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="n">
-        <v>48</v>
-      </c>
-      <c r="I6" t="n">
-        <v>67</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>69</v>
-      </c>
-      <c r="O6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>78</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -6136,22 +6013,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
@@ -6160,31 +6037,31 @@
         <v>43</v>
       </c>
       <c r="I7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J7" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.675</v>
+        <v>0.595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.675</v>
+        <v>0.595</v>
       </c>
       <c r="M7" t="n">
         <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O7" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="P7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Q7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -6198,19 +6075,19 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -6249,16 +6126,16 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
         <v>25</v>
@@ -6269,28 +6146,28 @@
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="n">
-        <v>0.665</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="L9" t="n">
-        <v>0.335</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>67.1</v>
+        <v>67.525</v>
       </c>
       <c r="O9" t="n">
-        <v>69</v>
+        <v>61.25</v>
       </c>
       <c r="P9" t="n">
-        <v>69</v>
+        <v>69.8</v>
       </c>
       <c r="Q9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -6304,19 +6181,19 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" t="s">
         <v>71</v>
-      </c>
-      <c r="E10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F10" t="s">
-        <v>73</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -6326,28 +6203,28 @@
       </c>
       <c r="I10"/>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08</v>
+        <v>0.135</v>
       </c>
       <c r="L10" t="n">
-        <v>0.92</v>
+        <v>0.855</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="O10" t="n">
-        <v>59.75</v>
+        <v>59.3</v>
       </c>
       <c r="P10" t="n">
         <v>71</v>
       </c>
       <c r="Q10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
@@ -6358,22 +6235,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
@@ -6405,22 +6282,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
@@ -6437,7 +6314,7 @@
       <c r="O12"/>
       <c r="P12"/>
       <c r="Q12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R12" t="b">
         <v>0</v>
@@ -6448,22 +6325,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
         <v>71</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" t="s">
-        <v>73</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
@@ -6480,7 +6357,7 @@
       <c r="O13"/>
       <c r="P13"/>
       <c r="Q13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -6491,22 +6368,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
         <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
@@ -6542,53 +6419,53 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
         <v>23</v>
       </c>
       <c r="H15" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="K15" t="n">
-        <v>0.345</v>
+        <v>0.29</v>
       </c>
       <c r="L15" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>57.8</v>
+        <v>46</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>3.425</v>
       </c>
       <c r="P15" t="n">
-        <v>59.7</v>
+        <v>66.575</v>
       </c>
       <c r="Q15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R15" t="b">
         <v>0</v>
@@ -6599,53 +6476,53 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" t="s">
         <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
       </c>
       <c r="G16" t="s">
         <v>23</v>
       </c>
       <c r="H16" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I16"/>
       <c r="J16" t="n">
-        <v>0.795</v>
+        <v>0.715</v>
       </c>
       <c r="K16" t="n">
-        <v>0.33</v>
+        <v>0.375</v>
       </c>
       <c r="L16" t="n">
-        <v>0.465</v>
+        <v>0.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="N16" t="n">
-        <v>46.05</v>
+        <v>47</v>
       </c>
       <c r="O16" t="n">
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>64.375</v>
+        <v>54.8999999999999</v>
       </c>
       <c r="Q16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R16" t="b">
         <v>0</v>
@@ -6659,19 +6536,19 @@
         <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
         <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
         <v>22</v>
@@ -6712,19 +6589,19 @@
         <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s">
         <v>22</v>
@@ -6743,7 +6620,7 @@
       <c r="O18"/>
       <c r="P18"/>
       <c r="Q18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R18" t="b">
         <v>0</v>
@@ -6757,19 +6634,19 @@
         <v>82</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G19" t="s">
         <v>22</v>
@@ -6788,7 +6665,7 @@
       <c r="O19"/>
       <c r="P19"/>
       <c r="Q19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R19" t="b">
         <v>0</v>
@@ -6802,19 +6679,19 @@
         <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G20" t="s">
         <v>22</v>
@@ -6855,19 +6732,19 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
         <v>22</v>
@@ -6886,7 +6763,7 @@
       <c r="O21"/>
       <c r="P21"/>
       <c r="Q21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -6900,19 +6777,19 @@
         <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
         <v>22</v>
@@ -6931,7 +6808,7 @@
       <c r="O22"/>
       <c r="P22"/>
       <c r="Q22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -6945,19 +6822,19 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
         <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
@@ -6992,19 +6869,19 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
@@ -7021,7 +6898,7 @@
       <c r="O24"/>
       <c r="P24"/>
       <c r="Q24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -7035,19 +6912,19 @@
         <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
       </c>
       <c r="D25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" t="s">
         <v>71</v>
-      </c>
-      <c r="E25" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" t="s">
-        <v>73</v>
       </c>
       <c r="G25" t="s">
         <v>23</v>
@@ -7064,7 +6941,7 @@
       <c r="O25"/>
       <c r="P25"/>
       <c r="Q25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -7078,19 +6955,19 @@
         <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
         <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
         <v>22</v>
@@ -7131,19 +7008,19 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
         <v>22</v>
@@ -7162,7 +7039,7 @@
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R27" t="b">
         <v>0</v>
@@ -7176,19 +7053,19 @@
         <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
@@ -7207,7 +7084,7 @@
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R28" t="b">
         <v>0</v>
@@ -7218,22 +7095,22 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
         <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G29" t="s">
         <v>22</v>
@@ -7271,22 +7148,22 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G30" t="s">
         <v>22</v>
@@ -7305,7 +7182,7 @@
       <c r="O30"/>
       <c r="P30"/>
       <c r="Q30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R30" t="b">
         <v>0</v>
@@ -7316,22 +7193,22 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
         <v>22</v>
@@ -7350,7 +7227,7 @@
       <c r="O31"/>
       <c r="P31"/>
       <c r="Q31" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R31" t="b">
         <v>0</v>
@@ -7361,22 +7238,22 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
         <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
         <v>22</v>
@@ -7414,22 +7291,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
         <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
         <v>22</v>
@@ -7448,7 +7325,7 @@
       <c r="O33"/>
       <c r="P33"/>
       <c r="Q33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R33" t="b">
         <v>0</v>
@@ -7459,22 +7336,22 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
         <v>22</v>
@@ -7483,7 +7360,7 @@
         <v>9</v>
       </c>
       <c r="I34" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J34"/>
       <c r="K34"/>
@@ -7493,7 +7370,7 @@
       <c r="O34"/>
       <c r="P34"/>
       <c r="Q34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R34" t="b">
         <v>0</v>
@@ -7504,22 +7381,22 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
         <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F35" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
         <v>23</v>
@@ -7551,22 +7428,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
         <v>23</v>
@@ -7583,7 +7460,7 @@
       <c r="O36"/>
       <c r="P36"/>
       <c r="Q36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R36" t="b">
         <v>0</v>
@@ -7594,22 +7471,22 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F37" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G37" t="s">
         <v>22</v>
@@ -7628,7 +7505,7 @@
       <c r="O37"/>
       <c r="P37"/>
       <c r="Q37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R37" t="b">
         <v>0</v>
@@ -7639,22 +7516,22 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
         <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G38" t="s">
         <v>22</v>
@@ -7692,22 +7569,22 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G39" t="s">
         <v>22</v>
@@ -7722,10 +7599,10 @@
         <v>0.9</v>
       </c>
       <c r="K39" t="n">
-        <v>0.83</v>
+        <v>0.845</v>
       </c>
       <c r="L39" t="n">
-        <v>0.83</v>
+        <v>0.845</v>
       </c>
       <c r="M39" t="n">
         <v>3</v>
@@ -7734,13 +7611,13 @@
         <v>35</v>
       </c>
       <c r="O39" t="n">
-        <v>5.125</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>63.75</v>
+        <v>58.6</v>
       </c>
       <c r="Q39" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R39" t="b">
         <v>0</v>
@@ -7751,55 +7628,55 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G40" t="s">
         <v>22</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>0.72</v>
+        <v>0.775</v>
       </c>
       <c r="K40" t="n">
-        <v>0.52</v>
+        <v>0.635</v>
       </c>
       <c r="L40" t="n">
-        <v>0.52</v>
+        <v>0.635</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="N40" t="n">
-        <v>46.425</v>
+        <v>45.15</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>68.425</v>
+        <v>59.85</v>
       </c>
       <c r="Q40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
@@ -7813,16 +7690,16 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
         <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F41" t="s">
         <v>87</v>
@@ -7862,16 +7739,16 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
         <v>87</v>
@@ -7882,13 +7759,13 @@
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" t="n">
-        <v>0.13</v>
+        <v>0.145</v>
       </c>
       <c r="K42" t="n">
-        <v>0.13</v>
+        <v>0.145</v>
       </c>
       <c r="L42" t="n">
-        <v>0.87</v>
+        <v>0.855</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -7903,7 +7780,7 @@
         <v>4</v>
       </c>
       <c r="Q42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R42" t="b">
         <v>0</v>
@@ -7917,16 +7794,16 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
         <v>87</v>
@@ -7937,19 +7814,19 @@
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" t="n">
-        <v>0.58</v>
+        <v>0.645</v>
       </c>
       <c r="K43" t="n">
-        <v>0.58</v>
+        <v>0.645</v>
       </c>
       <c r="L43" t="n">
-        <v>0.42</v>
+        <v>0.355</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>24.125</v>
+        <v>25</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -7958,7 +7835,7 @@
         <v>29</v>
       </c>
       <c r="Q43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R43" t="b">
         <v>0</v>
@@ -7969,22 +7846,22 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
         <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G44" t="s">
         <v>22</v>
@@ -8022,22 +7899,22 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G45" t="s">
         <v>22</v>
@@ -8056,7 +7933,7 @@
       <c r="O45"/>
       <c r="P45"/>
       <c r="Q45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R45" t="b">
         <v>0</v>
@@ -8067,22 +7944,22 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G46" t="s">
         <v>22</v>
@@ -8101,7 +7978,7 @@
       <c r="O46"/>
       <c r="P46"/>
       <c r="Q46" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R46" t="b">
         <v>0</v>
@@ -8112,22 +7989,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
         <v>93</v>
       </c>
       <c r="D47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
@@ -8159,22 +8036,22 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E48" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G48" t="s">
         <v>23</v>
@@ -8191,7 +8068,7 @@
       <c r="O48"/>
       <c r="P48"/>
       <c r="Q48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R48" t="b">
         <v>0</v>
@@ -8202,22 +8079,22 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
         <v>12</v>
       </c>
       <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>70</v>
+      </c>
+      <c r="F49" t="s">
         <v>71</v>
-      </c>
-      <c r="E49" t="s">
-        <v>72</v>
-      </c>
-      <c r="F49" t="s">
-        <v>73</v>
       </c>
       <c r="G49" t="s">
         <v>23</v>
@@ -8234,7 +8111,7 @@
       <c r="O49"/>
       <c r="P49"/>
       <c r="Q49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R49" t="b">
         <v>0</v>
@@ -8248,19 +8125,19 @@
         <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
         <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
@@ -8301,19 +8178,19 @@
         <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G51" t="s">
         <v>22</v>
@@ -8332,7 +8209,7 @@
       <c r="O51"/>
       <c r="P51"/>
       <c r="Q51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R51" t="b">
         <v>0</v>
@@ -8346,19 +8223,19 @@
         <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F52" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G52" t="s">
         <v>22</v>
@@ -8377,7 +8254,7 @@
       <c r="O52"/>
       <c r="P52"/>
       <c r="Q52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R52" t="b">
         <v>0</v>
@@ -8391,16 +8268,16 @@
         <v>90</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
         <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F53" t="s">
         <v>25</v>
@@ -8432,16 +8309,16 @@
         <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
       </c>
       <c r="D54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
@@ -8459,7 +8336,7 @@
       <c r="O54"/>
       <c r="P54"/>
       <c r="Q54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R54" t="b">
         <v>0</v>
@@ -8473,16 +8350,16 @@
         <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -8500,7 +8377,7 @@
       <c r="O55"/>
       <c r="P55"/>
       <c r="Q55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R55" t="b">
         <v>0</v>
@@ -8511,22 +8388,22 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
         <v>93</v>
       </c>
       <c r="D56" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F56" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G56" t="s">
         <v>22</v>
@@ -8564,22 +8441,22 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
         <v>11</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G57" t="s">
         <v>22</v>
@@ -8598,7 +8475,7 @@
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R57" t="b">
         <v>0</v>
@@ -8609,22 +8486,22 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E58" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G58" t="s">
         <v>22</v>
@@ -8643,7 +8520,7 @@
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R58" t="b">
         <v>0</v>
@@ -8657,19 +8534,19 @@
         <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
         <v>93</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G59" t="s">
         <v>23</v>
@@ -8708,19 +8585,19 @@
         <v>91</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C60" t="s">
         <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G60" t="s">
         <v>23</v>
@@ -8730,28 +8607,28 @@
       </c>
       <c r="I60"/>
       <c r="J60" t="n">
-        <v>0.77</v>
+        <v>0.765</v>
       </c>
       <c r="K60" t="n">
-        <v>0.275</v>
+        <v>0.22</v>
       </c>
       <c r="L60" t="n">
-        <v>0.495</v>
+        <v>0.545</v>
       </c>
       <c r="M60" t="n">
-        <v>5.825</v>
+        <v>6</v>
       </c>
       <c r="N60" t="n">
         <v>66</v>
       </c>
       <c r="O60" t="n">
-        <v>41.7</v>
+        <v>40.65</v>
       </c>
       <c r="P60" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R60" t="b">
         <v>0</v>
@@ -8765,19 +8642,19 @@
         <v>91</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
       </c>
       <c r="D61" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" t="s">
+        <v>70</v>
+      </c>
+      <c r="F61" t="s">
         <v>71</v>
-      </c>
-      <c r="E61" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" t="s">
-        <v>73</v>
       </c>
       <c r="G61" t="s">
         <v>23</v>
@@ -8787,28 +8664,28 @@
       </c>
       <c r="I61"/>
       <c r="J61" t="n">
-        <v>0.785</v>
+        <v>0.86</v>
       </c>
       <c r="K61" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L61" t="n">
-        <v>0.435</v>
+        <v>0.56</v>
       </c>
       <c r="M61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N61" t="n">
         <v>66</v>
       </c>
       <c r="O61" t="n">
-        <v>18.7</v>
+        <v>61</v>
       </c>
       <c r="P61" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="R61" t="b">
         <v>0</v>
@@ -8819,22 +8696,22 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s">
         <v>93</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F62" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G62" t="s">
         <v>22</v>
@@ -8872,22 +8749,22 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E63" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F63" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G63" t="s">
         <v>22</v>
@@ -8906,7 +8783,7 @@
       <c r="O63"/>
       <c r="P63"/>
       <c r="Q63" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R63" t="b">
         <v>0</v>
@@ -8917,22 +8794,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G64" t="s">
         <v>22</v>
@@ -8951,7 +8828,7 @@
       <c r="O64"/>
       <c r="P64"/>
       <c r="Q64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="R64" t="b">
         <v>0</v>
@@ -8962,22 +8839,22 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
         <v>93</v>
       </c>
       <c r="D65" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G65" t="s">
         <v>23</v>
@@ -9013,36 +8890,38 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s">
         <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F66" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="G66" t="s">
-        <v>25</v>
-      </c>
-      <c r="H66"/>
+        <v>23</v>
+      </c>
+      <c r="H66" t="n">
+        <v>31</v>
+      </c>
       <c r="I66"/>
       <c r="J66" t="n">
-        <v>0.545</v>
+        <v>0.635</v>
       </c>
       <c r="K66" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="L66" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="M66" t="n">
         <v>5</v>
@@ -9051,13 +8930,13 @@
         <v>61</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="P66" t="n">
         <v>67</v>
       </c>
       <c r="Q66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R66" t="b">
         <v>0</v>
@@ -9068,19 +8947,19 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F67" t="s">
         <v>25</v>
@@ -9091,28 +8970,28 @@
       <c r="H67"/>
       <c r="I67"/>
       <c r="J67" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="K67" t="n">
-        <v>0.205</v>
+        <v>0.195</v>
       </c>
       <c r="L67" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="M67" t="n">
-        <v>6</v>
+        <v>5.225</v>
       </c>
       <c r="N67" t="n">
-        <v>59.925</v>
+        <v>66</v>
       </c>
       <c r="O67" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="P67" t="n">
         <v>67</v>
       </c>
       <c r="Q67" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R67" t="b">
         <v>0</v>
@@ -9123,22 +9002,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
         <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E68" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G68" t="s">
         <v>22</v>
@@ -9176,19 +9055,19 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F69" t="s">
         <v>25</v>
@@ -9199,28 +9078,28 @@
       <c r="H69"/>
       <c r="I69"/>
       <c r="J69" t="n">
-        <v>0.375</v>
+        <v>0.29</v>
       </c>
       <c r="K69" t="n">
-        <v>0.21</v>
+        <v>0.165</v>
       </c>
       <c r="L69" t="n">
-        <v>0.465</v>
+        <v>0.495</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O69" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="P69" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R69" t="b">
         <v>0</v>
@@ -9231,38 +9110,40 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E70" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" t="n">
-        <v>36</v>
-      </c>
-      <c r="I70"/>
+        <v>31</v>
+      </c>
+      <c r="I70" t="n">
+        <v>37</v>
+      </c>
       <c r="J70" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="K70" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="L70" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="M70" t="n">
         <v>27</v>
@@ -9277,7 +9158,7 @@
         <v>57</v>
       </c>
       <c r="Q70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R70" t="b">
         <v>0</v>
@@ -9291,19 +9172,19 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C71" t="s">
         <v>93</v>
       </c>
       <c r="D71" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E71" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F71" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G71" t="s">
         <v>22</v>
@@ -9344,19 +9225,19 @@
         <v>92</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E72" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G72" t="s">
         <v>22</v>
@@ -9375,7 +9256,7 @@
       <c r="O72"/>
       <c r="P72"/>
       <c r="Q72" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R72" t="b">
         <v>0</v>
@@ -9389,19 +9270,19 @@
         <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E73" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F73" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G73" t="s">
         <v>22</v>
@@ -9420,7 +9301,7 @@
       <c r="O73"/>
       <c r="P73"/>
       <c r="Q73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="R73" t="b">
         <v>0</v>
